--- a/red_book/excel/笔记列表明细表-20260914.xlsx
+++ b/red_book/excel/笔记列表明细表-20260914.xlsx
@@ -95,7 +95,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.0" customWidth="true"/>
@@ -314,19 +314,19 @@
         <v>53136.0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3554.0</v>
+        <v>3704.0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.064</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>17.0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>9.0</v>
@@ -361,7 +361,7 @@
         <v>2229.0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1311.0</v>
+        <v>1313.0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.044</v>
@@ -408,13 +408,13 @@
         <v>9775.0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1901.0</v>
+        <v>1924.0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.083</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0.0</v>
@@ -455,7 +455,7 @@
         <v>8361.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1621.0</v>
+        <v>1647.0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.195</v>
@@ -620,6 +620,241 @@
         <v>37.0</v>
       </c>
       <c r="M10" s="2" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11" customHeight="true" ht="20.0">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>加装内存条保密级教程，零基础宝妈自己搞定</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026年08月13日13时08分19秒</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>图文</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>29996.0</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>5035.0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>147.0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>139.0</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12" customHeight="true" ht="20.0">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>我理解汪峰，但我害怕成为那700人</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026年08月11日13时33分21秒</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>图文</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>442.0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="13" customHeight="true" ht="20.0">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>电子玩具充不进电？别扔，换块电池就行</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026年08月10日12时51分36秒</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>图文</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2814.0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>199.0</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14" customHeight="true" ht="20.0">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>门把手松动？别叫师傅！4种故障轻松搞定</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026年08月08日13时05分14秒</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>图文</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>28628.0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2982.0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>87.0</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="true" ht="20.0">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>二胎宝妈如何0元修好点读笔</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026年08月07日12时19分17秒</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>图文</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1854.0</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>162.0</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.088</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="M15" s="2" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/red_book/excel/笔记列表明细表-20260914.xlsx
+++ b/red_book/excel/笔记列表明细表-20260914.xlsx
@@ -455,7 +455,7 @@
         <v>8361.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1647.0</v>
+        <v>1648.0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.195</v>
@@ -643,7 +643,7 @@
         <v>29996.0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5035.0</v>
+        <v>5036.0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0.164</v>

--- a/red_book/excel/笔记列表明细表-20260914.xlsx
+++ b/red_book/excel/笔记列表明细表-20260914.xlsx
@@ -95,7 +95,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.0" customWidth="true"/>
@@ -314,19 +314,19 @@
         <v>53136.0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3704.0</v>
+        <v>3554.0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.064</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>37.0</v>
+        <v>35.0</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>17.0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>9.0</v>
@@ -361,7 +361,7 @@
         <v>2229.0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1313.0</v>
+        <v>1311.0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.044</v>
@@ -408,13 +408,13 @@
         <v>9775.0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1924.0</v>
+        <v>1901.0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.083</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>36.0</v>
+        <v>34.0</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0.0</v>
@@ -455,7 +455,7 @@
         <v>8361.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1648.0</v>
+        <v>1621.0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.195</v>
@@ -620,241 +620,6 @@
         <v>37.0</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="11" customHeight="true" ht="20.0">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>加装内存条保密级教程，零基础宝妈自己搞定</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026年08月13日13时08分19秒</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>图文</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>29996.0</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>5036.0</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>147.0</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>139.0</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>43.0</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="12" customHeight="true" ht="20.0">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>我理解汪峰，但我害怕成为那700人</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>2026年08月11日13时33分21秒</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>图文</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>442.0</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="13" customHeight="true" ht="20.0">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>电子玩具充不进电？别扔，换块电池就行</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2026年08月10日12时51分36秒</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>图文</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>2814.0</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>199.0</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>69.0</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="14" customHeight="true" ht="20.0">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>门把手松动？别叫师傅！4种故障轻松搞定</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>2026年08月08日13时05分14秒</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>图文</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>28628.0</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>2982.0</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>87.0</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="15" customHeight="true" ht="20.0">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>二胎宝妈如何0元修好点读笔</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>2026年08月07日12时19分17秒</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>图文</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>1854.0</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>162.0</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.088</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="M15" s="2" t="n">
         <v>0.0</v>
       </c>
     </row>
